--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125888745</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>100413</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583815</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964006</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B4" t="n">
-        <v>100413</v>
+        <v>80070</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>101410</v>
+        <v>100413</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R25" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>100413</v>
+        <v>101410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R26" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3588,6 +3588,491 @@
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>125897322</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98362</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>583974</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6963977</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>125897314</v>
+      </c>
+      <c r="B33" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>658</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>583871</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6963899</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>125897313</v>
+      </c>
+      <c r="B34" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>658</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>583852</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6963923</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>125897326</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80070</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>583888</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6963889</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>125897312</v>
+      </c>
+      <c r="B36" t="n">
+        <v>91517</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>658</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>583853</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6963924</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>100413</v>
+        <v>80070</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R2" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,7 +775,7 @@
         <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>97400</v>
+        <v>97407</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125887351</v>
+        <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>80070</v>
+        <v>100420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584020</v>
+        <v>583815</v>
       </c>
       <c r="R4" t="n">
-        <v>6963947</v>
+        <v>6964006</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96577</v>
+        <v>96584</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>100413</v>
+        <v>80070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>101410</v>
+        <v>100420</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R9" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>80070</v>
+        <v>101417</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R10" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887998</v>
+        <v>125887805</v>
       </c>
       <c r="B11" t="n">
-        <v>96577</v>
+        <v>98365</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583908</v>
+        <v>583985</v>
       </c>
       <c r="R11" t="n">
-        <v>6963955</v>
+        <v>6963958</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887805</v>
+        <v>125887998</v>
       </c>
       <c r="B12" t="n">
-        <v>98358</v>
+        <v>96584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583985</v>
+        <v>583908</v>
       </c>
       <c r="R12" t="n">
-        <v>6963958</v>
+        <v>6963955</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1750,7 +1750,7 @@
         <v>125888398</v>
       </c>
       <c r="B13" t="n">
-        <v>91185</v>
+        <v>91192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888356</v>
+        <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>100413</v>
+        <v>80070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583872</v>
+        <v>583880</v>
       </c>
       <c r="R14" t="n">
-        <v>6963914</v>
+        <v>6963893</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125888464</v>
+        <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>80070</v>
+        <v>79974</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583880</v>
+        <v>583905</v>
       </c>
       <c r="R15" t="n">
-        <v>6963893</v>
+        <v>6963925</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125887945</v>
+        <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>79974</v>
+        <v>100420</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583905</v>
+        <v>583872</v>
       </c>
       <c r="R16" t="n">
-        <v>6963925</v>
+        <v>6963914</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>101417</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R20" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888364</v>
+        <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>101410</v>
+        <v>91520</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583875</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6963907</v>
+        <v>6963929</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897311</v>
+        <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>91513</v>
+        <v>80070</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583836</v>
+        <v>583915</v>
       </c>
       <c r="R22" t="n">
-        <v>6963929</v>
+        <v>6963958</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B23" t="n">
-        <v>80070</v>
+        <v>80030</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R23" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B24" t="n">
-        <v>80030</v>
+        <v>80070</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R24" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2914,7 +2914,7 @@
         <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>100413</v>
+        <v>100420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101410</v>
+        <v>101417</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97400</v>
+        <v>97407</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>98362</v>
+        <v>91520</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R32" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>91517</v>
+        <v>98365</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R33" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3787,7 +3787,7 @@
         <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>91517</v>
+        <v>91520</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>80070</v>
+        <v>91520</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R35" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897312</v>
+        <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>91517</v>
+        <v>80070</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583853</v>
+        <v>583888</v>
       </c>
       <c r="R36" t="n">
-        <v>6963924</v>
+        <v>6963889</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4072,6 +4072,200 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>125943980</v>
+      </c>
+      <c r="B37" t="n">
+        <v>100420</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>584002</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6963978</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>125943979</v>
+      </c>
+      <c r="B38" t="n">
+        <v>100420</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>583989</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6963983</v>
+      </c>
+      <c r="S38" t="n">
+        <v>25</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>97407</v>
+        <v>100420</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R3" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125897309</v>
       </c>
       <c r="B4" t="n">
-        <v>100420</v>
+        <v>97407</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>583962</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6964012</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125897300</v>
+        <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>100420</v>
+        <v>101417</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584030</v>
+        <v>583983</v>
       </c>
       <c r="R9" t="n">
-        <v>6963845</v>
+        <v>6963951</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>101417</v>
+        <v>100420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R10" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -2135,48 +2135,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125888114</v>
+        <v>125897304</v>
       </c>
       <c r="B17" t="n">
-        <v>80070</v>
+        <v>100420</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583879</v>
+        <v>583848</v>
       </c>
       <c r="R17" t="n">
-        <v>6963918</v>
+        <v>6964006</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125888045</v>
+        <v>125888114</v>
       </c>
       <c r="B18" t="n">
         <v>80070</v>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583895</v>
+        <v>583879</v>
       </c>
       <c r="R18" t="n">
-        <v>6963945</v>
+        <v>6963918</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2329,48 +2329,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125897304</v>
+        <v>125888045</v>
       </c>
       <c r="B19" t="n">
-        <v>100420</v>
+        <v>80070</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583848</v>
+        <v>583895</v>
       </c>
       <c r="R19" t="n">
-        <v>6964006</v>
+        <v>6963945</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B20" t="n">
-        <v>101417</v>
+        <v>80070</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R20" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897311</v>
+        <v>125888364</v>
       </c>
       <c r="B21" t="n">
-        <v>91520</v>
+        <v>101417</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583875</v>
       </c>
       <c r="R21" t="n">
-        <v>6963929</v>
+        <v>6963907</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888002</v>
+        <v>125897311</v>
       </c>
       <c r="B22" t="n">
-        <v>80070</v>
+        <v>91520</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583915</v>
+        <v>583836</v>
       </c>
       <c r="R22" t="n">
-        <v>6963958</v>
+        <v>6963929</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>100420</v>
+        <v>101417</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R25" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>101417</v>
+        <v>100420</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R26" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B32" t="n">
-        <v>91520</v>
+        <v>98365</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R32" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B33" t="n">
-        <v>98365</v>
+        <v>91520</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R33" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125888745</v>
+        <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>100420</v>
+        <v>97408</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583815</v>
+        <v>583962</v>
       </c>
       <c r="R3" t="n">
-        <v>6964006</v>
+        <v>6964012</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>97407</v>
+        <v>100421</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R4" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>125888015</v>
       </c>
       <c r="B5" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125888183</v>
       </c>
       <c r="B6" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96584</v>
+        <v>96585</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>101417</v>
+        <v>100421</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R9" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125897300</v>
+        <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>100420</v>
+        <v>101418</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584030</v>
+        <v>583983</v>
       </c>
       <c r="R10" t="n">
-        <v>6963845</v>
+        <v>6963951</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>91193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R11" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1653,7 +1653,7 @@
         <v>125887998</v>
       </c>
       <c r="B12" t="n">
-        <v>96584</v>
+        <v>96585</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>91192</v>
+        <v>98366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R13" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1847,7 +1847,7 @@
         <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>100420</v>
+        <v>100421</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,48 +2135,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125897304</v>
+        <v>125888114</v>
       </c>
       <c r="B17" t="n">
-        <v>100420</v>
+        <v>80071</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583848</v>
+        <v>583879</v>
       </c>
       <c r="R17" t="n">
-        <v>6964006</v>
+        <v>6963918</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125888114</v>
+        <v>125888045</v>
       </c>
       <c r="B18" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583879</v>
+        <v>583895</v>
       </c>
       <c r="R18" t="n">
-        <v>6963918</v>
+        <v>6963945</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2329,48 +2329,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125888045</v>
+        <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>80070</v>
+        <v>100421</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583895</v>
+        <v>583848</v>
       </c>
       <c r="R19" t="n">
-        <v>6963945</v>
+        <v>6964006</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>125888002</v>
       </c>
       <c r="B20" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888364</v>
+        <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>101417</v>
+        <v>91521</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583875</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6963907</v>
+        <v>6963929</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,48 +2620,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897311</v>
+        <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>91520</v>
+        <v>101418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583836</v>
+        <v>583875</v>
       </c>
       <c r="R22" t="n">
-        <v>6963929</v>
+        <v>6963907</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80030</v>
+        <v>80071</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R23" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80070</v>
+        <v>80031</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R24" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>101417</v>
+        <v>100421</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R25" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>100420</v>
+        <v>101418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R26" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101417</v>
+        <v>101418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80030</v>
+        <v>80031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97407</v>
+        <v>97408</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125887737</v>
       </c>
       <c r="B31" t="n">
-        <v>80099</v>
+        <v>80100</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>98365</v>
+        <v>91521</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R32" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>91520</v>
+        <v>98366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R33" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897313</v>
+        <v>125897326</v>
       </c>
       <c r="B34" t="n">
-        <v>91520</v>
+        <v>80071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583852</v>
+        <v>583888</v>
       </c>
       <c r="R34" t="n">
-        <v>6963923</v>
+        <v>6963889</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897312</v>
+        <v>125897313</v>
       </c>
       <c r="B35" t="n">
-        <v>91520</v>
+        <v>91521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583853</v>
+        <v>583852</v>
       </c>
       <c r="R35" t="n">
-        <v>6963924</v>
+        <v>6963923</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B36" t="n">
-        <v>80070</v>
+        <v>91521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R36" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100420</v>
+        <v>100421</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100420</v>
+        <v>100421</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125888745</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>100423</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583815</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964006</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +780,7 @@
         <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>97408</v>
+        <v>97410</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B4" t="n">
-        <v>100421</v>
+        <v>80071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96585</v>
+        <v>96587</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>101418</v>
+        <v>101420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125888398</v>
+        <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>91193</v>
+        <v>96587</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583876</v>
+        <v>583908</v>
       </c>
       <c r="R11" t="n">
-        <v>6963902</v>
+        <v>6963955</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887998</v>
+        <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>96585</v>
+        <v>91193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583908</v>
+        <v>583876</v>
       </c>
       <c r="R12" t="n">
-        <v>6963955</v>
+        <v>6963902</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1750,7 +1750,7 @@
         <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>98366</v>
+        <v>98368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888002</v>
+        <v>125897311</v>
       </c>
       <c r="B20" t="n">
-        <v>80071</v>
+        <v>91524</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,37 +2437,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583915</v>
+        <v>583836</v>
       </c>
       <c r="R20" t="n">
-        <v>6963958</v>
+        <v>6963929</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897311</v>
+        <v>125888002</v>
       </c>
       <c r="B21" t="n">
-        <v>91521</v>
+        <v>80071</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,37 +2534,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583915</v>
       </c>
       <c r="R21" t="n">
-        <v>6963929</v>
+        <v>6963958</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>101418</v>
+        <v>101420</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>100421</v>
+        <v>101420</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R25" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>101418</v>
+        <v>100423</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R26" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101418</v>
+        <v>101420</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97408</v>
+        <v>97410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B32" t="n">
-        <v>91521</v>
+        <v>98368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R32" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B33" t="n">
-        <v>98366</v>
+        <v>91524</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R33" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B34" t="n">
-        <v>80071</v>
+        <v>91524</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R34" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3884,7 +3884,7 @@
         <v>125897313</v>
       </c>
       <c r="B35" t="n">
-        <v>91521</v>
+        <v>91524</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897312</v>
+        <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>91521</v>
+        <v>80071</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583853</v>
+        <v>583888</v>
       </c>
       <c r="R36" t="n">
-        <v>6963924</v>
+        <v>6963889</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100421</v>
+        <v>100423</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>100423</v>
+        <v>80071</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R2" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>97410</v>
+        <v>100423</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R3" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,48 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B4" t="n">
-        <v>80071</v>
+        <v>97410</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R4" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>98368</v>
+        <v>91524</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R32" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>91524</v>
+        <v>98368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R33" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>80071</v>
+        <v>97414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B3" t="n">
-        <v>100423</v>
+        <v>80075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R3" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>97410</v>
+        <v>100427</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R4" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>125888015</v>
       </c>
       <c r="B5" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125888183</v>
       </c>
       <c r="B6" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96587</v>
+        <v>96591</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125897300</v>
+        <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>100423</v>
+        <v>101424</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584030</v>
+        <v>583983</v>
       </c>
       <c r="R9" t="n">
-        <v>6963845</v>
+        <v>6963951</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>101420</v>
+        <v>100427</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R10" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887998</v>
+        <v>125888398</v>
       </c>
       <c r="B11" t="n">
-        <v>96587</v>
+        <v>91197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583908</v>
+        <v>583876</v>
       </c>
       <c r="R11" t="n">
-        <v>6963955</v>
+        <v>6963902</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125888398</v>
+        <v>125887998</v>
       </c>
       <c r="B12" t="n">
-        <v>91193</v>
+        <v>96591</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583876</v>
+        <v>583908</v>
       </c>
       <c r="R12" t="n">
-        <v>6963902</v>
+        <v>6963955</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1750,7 +1750,7 @@
         <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888464</v>
+        <v>125888356</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>100427</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583880</v>
+        <v>583872</v>
       </c>
       <c r="R14" t="n">
-        <v>6963893</v>
+        <v>6963914</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125887945</v>
+        <v>125888464</v>
       </c>
       <c r="B15" t="n">
-        <v>79975</v>
+        <v>80075</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583905</v>
+        <v>583880</v>
       </c>
       <c r="R15" t="n">
-        <v>6963925</v>
+        <v>6963893</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125888356</v>
+        <v>125887945</v>
       </c>
       <c r="B16" t="n">
-        <v>100423</v>
+        <v>79979</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583872</v>
+        <v>583905</v>
       </c>
       <c r="R16" t="n">
-        <v>6963914</v>
+        <v>6963925</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>125888114</v>
       </c>
       <c r="B17" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125888045</v>
       </c>
       <c r="B18" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>125897311</v>
       </c>
       <c r="B20" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>125888002</v>
       </c>
       <c r="B21" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B23" t="n">
-        <v>80071</v>
+        <v>80035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R23" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B24" t="n">
-        <v>80031</v>
+        <v>80075</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R24" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2914,7 +2914,7 @@
         <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80071</v>
+        <v>80075</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80031</v>
+        <v>80035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97410</v>
+        <v>97414</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125887737</v>
       </c>
       <c r="B31" t="n">
-        <v>80100</v>
+        <v>80104</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>98368</v>
+        <v>98372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125897312</v>
       </c>
       <c r="B34" t="n">
-        <v>91524</v>
+        <v>91528</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897313</v>
+        <v>125897326</v>
       </c>
       <c r="B35" t="n">
-        <v>91524</v>
+        <v>80075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583852</v>
+        <v>583888</v>
       </c>
       <c r="R35" t="n">
-        <v>6963923</v>
+        <v>6963889</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897326</v>
+        <v>125897313</v>
       </c>
       <c r="B36" t="n">
-        <v>80071</v>
+        <v>91528</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583888</v>
+        <v>583852</v>
       </c>
       <c r="R36" t="n">
-        <v>6963889</v>
+        <v>6963923</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100423</v>
+        <v>100427</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125888398</v>
+        <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>91197</v>
+        <v>96591</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583876</v>
+        <v>583908</v>
       </c>
       <c r="R11" t="n">
-        <v>6963902</v>
+        <v>6963955</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887998</v>
+        <v>125887805</v>
       </c>
       <c r="B12" t="n">
-        <v>96591</v>
+        <v>98372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583908</v>
+        <v>583985</v>
       </c>
       <c r="R12" t="n">
-        <v>6963955</v>
+        <v>6963958</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B13" t="n">
-        <v>98372</v>
+        <v>91197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R13" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888356</v>
+        <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>100427</v>
+        <v>80075</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583872</v>
+        <v>583880</v>
       </c>
       <c r="R14" t="n">
-        <v>6963914</v>
+        <v>6963893</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125888464</v>
+        <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>80075</v>
+        <v>79979</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583880</v>
+        <v>583905</v>
       </c>
       <c r="R15" t="n">
-        <v>6963893</v>
+        <v>6963925</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125887945</v>
+        <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>79979</v>
+        <v>100427</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583905</v>
+        <v>583872</v>
       </c>
       <c r="R16" t="n">
-        <v>6963925</v>
+        <v>6963914</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3784,7 +3784,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897312</v>
+        <v>125897313</v>
       </c>
       <c r="B34" t="n">
         <v>91528</v>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583853</v>
+        <v>583852</v>
       </c>
       <c r="R34" t="n">
-        <v>6963924</v>
+        <v>6963923</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>80075</v>
+        <v>91528</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3892,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R35" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897313</v>
+        <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>91528</v>
+        <v>80075</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583852</v>
+        <v>583888</v>
       </c>
       <c r="R36" t="n">
-        <v>6963923</v>
+        <v>6963889</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125897309</v>
+        <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>97414</v>
+        <v>80075</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583962</v>
+        <v>584020</v>
       </c>
       <c r="R2" t="n">
-        <v>6964012</v>
+        <v>6963947</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>80075</v>
+        <v>97415</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R3" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>96591</v>
+        <v>96592</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125887805</v>
       </c>
       <c r="B12" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>101425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R21" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>101424</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R22" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80035</v>
+        <v>80075</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R23" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80075</v>
+        <v>80035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R24" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>101424</v>
+        <v>100428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R25" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>100427</v>
+        <v>101425</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R26" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97414</v>
+        <v>97415</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>98372</v>
+        <v>98373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897313</v>
+        <v>125897326</v>
       </c>
       <c r="B34" t="n">
-        <v>91528</v>
+        <v>80075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583852</v>
+        <v>583888</v>
       </c>
       <c r="R34" t="n">
-        <v>6963923</v>
+        <v>6963889</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897312</v>
+        <v>125897313</v>
       </c>
       <c r="B35" t="n">
         <v>91528</v>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583853</v>
+        <v>583852</v>
       </c>
       <c r="R35" t="n">
-        <v>6963924</v>
+        <v>6963923</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B36" t="n">
-        <v>80075</v>
+        <v>91528</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R36" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>98373</v>
+        <v>91197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R12" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>91197</v>
+        <v>98373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R13" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B21" t="n">
-        <v>101425</v>
+        <v>80075</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R21" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>101425</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R22" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>100428</v>
+        <v>101425</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R25" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>101425</v>
+        <v>100428</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R26" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B8" t="n">
-        <v>80075</v>
+        <v>101425</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R8" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125887667</v>
+        <v>125888370</v>
       </c>
       <c r="B9" t="n">
-        <v>101425</v>
+        <v>80075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583983</v>
+        <v>583875</v>
       </c>
       <c r="R9" t="n">
-        <v>6963951</v>
+        <v>6963902</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B21" t="n">
-        <v>80075</v>
+        <v>101425</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R21" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>101425</v>
+        <v>80075</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R22" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>101425</v>
+        <v>100428</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R25" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>100428</v>
+        <v>101425</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R26" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>97415</v>
+        <v>100430</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R3" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125897309</v>
       </c>
       <c r="B4" t="n">
-        <v>100428</v>
+        <v>97417</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>583962</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6964012</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,7 +974,7 @@
         <v>125888015</v>
       </c>
       <c r="B5" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125888183</v>
       </c>
       <c r="B6" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125887667</v>
+        <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>101425</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583983</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6963951</v>
+        <v>6963902</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>80075</v>
+        <v>101427</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R9" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1459,7 +1459,7 @@
         <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>96592</v>
+        <v>96594</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>91197</v>
+        <v>91199</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>98373</v>
+        <v>98375</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1847,7 +1847,7 @@
         <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         <v>125888114</v>
       </c>
       <c r="B17" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125888045</v>
       </c>
       <c r="B18" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,48 +2426,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125897311</v>
+        <v>125888364</v>
       </c>
       <c r="B20" t="n">
-        <v>91528</v>
+        <v>101427</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583836</v>
+        <v>583875</v>
       </c>
       <c r="R20" t="n">
-        <v>6963929</v>
+        <v>6963907</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888364</v>
+        <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>101425</v>
+        <v>91530</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583875</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6963907</v>
+        <v>6963929</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80075</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80035</v>
+        <v>80036</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97415</v>
+        <v>97417</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125887737</v>
       </c>
       <c r="B31" t="n">
-        <v>80104</v>
+        <v>80105</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B32" t="n">
-        <v>91528</v>
+        <v>98375</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R32" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B33" t="n">
-        <v>98373</v>
+        <v>91530</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R33" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897326</v>
+        <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>80075</v>
+        <v>91530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583888</v>
+        <v>583852</v>
       </c>
       <c r="R34" t="n">
-        <v>6963889</v>
+        <v>6963923</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897313</v>
+        <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>91528</v>
+        <v>91530</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583852</v>
+        <v>583853</v>
       </c>
       <c r="R35" t="n">
-        <v>6963923</v>
+        <v>6963924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897312</v>
+        <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>91528</v>
+        <v>80076</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583853</v>
+        <v>583888</v>
       </c>
       <c r="R36" t="n">
-        <v>6963924</v>
+        <v>6963889</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>97417</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -874,48 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125897309</v>
+        <v>125887351</v>
       </c>
       <c r="B4" t="n">
-        <v>97417</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583962</v>
+        <v>584020</v>
       </c>
       <c r="R4" t="n">
-        <v>6964012</v>
+        <v>6963947</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B12" t="n">
-        <v>91199</v>
+        <v>98375</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R12" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B13" t="n">
-        <v>98375</v>
+        <v>91199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R13" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B20" t="n">
-        <v>101427</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R20" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897311</v>
+        <v>125888364</v>
       </c>
       <c r="B21" t="n">
-        <v>91530</v>
+        <v>101427</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583875</v>
       </c>
       <c r="R21" t="n">
-        <v>6963929</v>
+        <v>6963907</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888002</v>
+        <v>125897311</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>91530</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583915</v>
+        <v>583836</v>
       </c>
       <c r="R22" t="n">
-        <v>6963958</v>
+        <v>6963929</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>97417</v>
+        <v>97419</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>101427</v>
+        <v>100432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R9" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125897300</v>
+        <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>100430</v>
+        <v>101429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584030</v>
+        <v>583983</v>
       </c>
       <c r="R10" t="n">
-        <v>6963845</v>
+        <v>6963951</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>96594</v>
+        <v>96596</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1650,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>98375</v>
+        <v>91201</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R12" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>91199</v>
+        <v>98377</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R13" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2041,7 +2041,7 @@
         <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>101429</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R20" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888364</v>
+        <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>101427</v>
+        <v>91532</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583875</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6963907</v>
+        <v>6963929</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125897311</v>
+        <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>91530</v>
+        <v>80076</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2631,37 +2631,37 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583836</v>
+        <v>583915</v>
       </c>
       <c r="R22" t="n">
-        <v>6963929</v>
+        <v>6963958</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>80036</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R23" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B24" t="n">
-        <v>80036</v>
+        <v>80076</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R24" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>100430</v>
+        <v>101429</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R25" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>101427</v>
+        <v>100432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R26" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97417</v>
+        <v>97419</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>98375</v>
+        <v>91532</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R32" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>91530</v>
+        <v>98377</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R33" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3787,7 +3787,7 @@
         <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>91530</v>
+        <v>91532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B2" t="n">
-        <v>97419</v>
+        <v>100432</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R2" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,32 +777,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B3" t="n">
-        <v>100432</v>
+        <v>80076</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R3" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,48 +874,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>97419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R4" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1262,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125888370</v>
+        <v>125897300</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>100432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583875</v>
+        <v>584030</v>
       </c>
       <c r="R8" t="n">
-        <v>6963902</v>
+        <v>6963845</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,48 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B9" t="n">
-        <v>100432</v>
+        <v>80076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R9" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80036</v>
+        <v>80076</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R23" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80076</v>
+        <v>80036</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R24" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887722</v>
+        <v>125887757</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>80036</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583991</v>
+        <v>583975</v>
       </c>
       <c r="R28" t="n">
-        <v>6963976</v>
+        <v>6963973</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887757</v>
+        <v>125887722</v>
       </c>
       <c r="B29" t="n">
-        <v>80036</v>
+        <v>80076</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583975</v>
+        <v>583991</v>
       </c>
       <c r="R29" t="n">
-        <v>6963973</v>
+        <v>6963976</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>100432</v>
+        <v>80076</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R2" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>80076</v>
+        <v>97421</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R3" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>97419</v>
+        <v>100434</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,37 +880,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R4" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>100432</v>
+        <v>80076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,48 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125888370</v>
+        <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>80076</v>
+        <v>100434</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583875</v>
+        <v>584030</v>
       </c>
       <c r="R9" t="n">
-        <v>6963902</v>
+        <v>6963845</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1556,7 +1556,7 @@
         <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>96596</v>
+        <v>96598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1653,7 +1653,7 @@
         <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>91201</v>
+        <v>91203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
         <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B20" t="n">
-        <v>101429</v>
+        <v>80076</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R20" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2526,7 +2526,7 @@
         <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>80076</v>
+        <v>101431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R22" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2914,7 +2914,7 @@
         <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101429</v>
+        <v>101431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887757</v>
+        <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80036</v>
+        <v>80076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583975</v>
+        <v>583991</v>
       </c>
       <c r="R28" t="n">
-        <v>6963973</v>
+        <v>6963976</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887722</v>
+        <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80076</v>
+        <v>80036</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583991</v>
+        <v>583975</v>
       </c>
       <c r="R29" t="n">
-        <v>6963976</v>
+        <v>6963973</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97419</v>
+        <v>97421</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>98377</v>
+        <v>98379</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>91532</v>
+        <v>91534</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100432</v>
+        <v>100434</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>80076</v>
+        <v>97421</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>97421</v>
+        <v>100434</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R3" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B4" t="n">
-        <v>100434</v>
+        <v>80076</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887998</v>
+        <v>125887805</v>
       </c>
       <c r="B11" t="n">
-        <v>96598</v>
+        <v>98379</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583908</v>
+        <v>583985</v>
       </c>
       <c r="R11" t="n">
-        <v>6963955</v>
+        <v>6963958</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125888398</v>
+        <v>125887998</v>
       </c>
       <c r="B12" t="n">
-        <v>91203</v>
+        <v>96598</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583876</v>
+        <v>583908</v>
       </c>
       <c r="R12" t="n">
-        <v>6963902</v>
+        <v>6963955</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B13" t="n">
-        <v>98379</v>
+        <v>91203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R13" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>97421</v>
+        <v>97425</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>125887351</v>
       </c>
       <c r="B4" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125888015</v>
       </c>
       <c r="B5" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125888183</v>
       </c>
       <c r="B6" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125888370</v>
+        <v>125897300</v>
       </c>
       <c r="B8" t="n">
-        <v>80076</v>
+        <v>100438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583875</v>
+        <v>584030</v>
       </c>
       <c r="R8" t="n">
-        <v>6963902</v>
+        <v>6963845</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,48 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B9" t="n">
-        <v>100434</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R9" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B11" t="n">
-        <v>98379</v>
+        <v>91207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R11" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1653,7 +1653,7 @@
         <v>125887998</v>
       </c>
       <c r="B12" t="n">
-        <v>96598</v>
+        <v>96602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>91203</v>
+        <v>98383</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R13" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888464</v>
+        <v>125888356</v>
       </c>
       <c r="B14" t="n">
-        <v>80076</v>
+        <v>100438</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583880</v>
+        <v>583872</v>
       </c>
       <c r="R14" t="n">
-        <v>6963893</v>
+        <v>6963914</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125887945</v>
+        <v>125888464</v>
       </c>
       <c r="B15" t="n">
-        <v>79980</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583905</v>
+        <v>583880</v>
       </c>
       <c r="R15" t="n">
-        <v>6963925</v>
+        <v>6963893</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125888356</v>
+        <v>125887945</v>
       </c>
       <c r="B16" t="n">
-        <v>100434</v>
+        <v>79984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583872</v>
+        <v>583905</v>
       </c>
       <c r="R16" t="n">
-        <v>6963914</v>
+        <v>6963925</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2138,7 +2138,7 @@
         <v>125888114</v>
       </c>
       <c r="B17" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         <v>125888045</v>
       </c>
       <c r="B18" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2429,7 +2429,7 @@
         <v>125888002</v>
       </c>
       <c r="B20" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3302,7 +3302,7 @@
         <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80036</v>
+        <v>80040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97421</v>
+        <v>97425</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125887737</v>
       </c>
       <c r="B31" t="n">
-        <v>80105</v>
+        <v>80109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B32" t="n">
-        <v>91534</v>
+        <v>98383</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R32" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B33" t="n">
-        <v>98379</v>
+        <v>91538</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R33" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3787,7 +3787,7 @@
         <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>91534</v>
+        <v>91538</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>80076</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125897309</v>
+        <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>97425</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583962</v>
+        <v>584020</v>
       </c>
       <c r="R2" t="n">
-        <v>6964012</v>
+        <v>6963947</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125888745</v>
+        <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>100438</v>
+        <v>97425</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583815</v>
+        <v>583962</v>
       </c>
       <c r="R3" t="n">
-        <v>6964006</v>
+        <v>6964012</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125887351</v>
+        <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>100438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584020</v>
+        <v>583815</v>
       </c>
       <c r="R4" t="n">
-        <v>6963947</v>
+        <v>6964006</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1262,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>100438</v>
+        <v>80080</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>101435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R9" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>101435</v>
+        <v>100438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R10" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888356</v>
+        <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>100438</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583872</v>
+        <v>583880</v>
       </c>
       <c r="R14" t="n">
-        <v>6963914</v>
+        <v>6963893</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125888464</v>
+        <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>79984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583880</v>
+        <v>583905</v>
       </c>
       <c r="R15" t="n">
-        <v>6963893</v>
+        <v>6963925</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125887945</v>
+        <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>79984</v>
+        <v>100438</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583905</v>
+        <v>583872</v>
       </c>
       <c r="R16" t="n">
-        <v>6963925</v>
+        <v>6963914</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>97428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B3" t="n">
-        <v>97425</v>
+        <v>100441</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R3" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -869,32 +874,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125887351</v>
       </c>
       <c r="B4" t="n">
-        <v>100438</v>
+        <v>80080</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>584020</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6963947</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96602</v>
+        <v>96605</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B11" t="n">
-        <v>91207</v>
+        <v>98386</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R11" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887998</v>
+        <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>96602</v>
+        <v>91207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583908</v>
+        <v>583876</v>
       </c>
       <c r="R12" t="n">
-        <v>6963955</v>
+        <v>6963902</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887805</v>
+        <v>125887998</v>
       </c>
       <c r="B13" t="n">
-        <v>98383</v>
+        <v>96605</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>53</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583985</v>
+        <v>583908</v>
       </c>
       <c r="R13" t="n">
-        <v>6963958</v>
+        <v>6963955</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888464</v>
+        <v>125888356</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>100441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583880</v>
+        <v>583872</v>
       </c>
       <c r="R14" t="n">
-        <v>6963893</v>
+        <v>6963914</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125887945</v>
+        <v>125888464</v>
       </c>
       <c r="B15" t="n">
-        <v>79984</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583905</v>
+        <v>583880</v>
       </c>
       <c r="R15" t="n">
-        <v>6963925</v>
+        <v>6963893</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125888356</v>
+        <v>125887945</v>
       </c>
       <c r="B16" t="n">
-        <v>100438</v>
+        <v>79984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583872</v>
+        <v>583905</v>
       </c>
       <c r="R16" t="n">
-        <v>6963914</v>
+        <v>6963925</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888002</v>
+        <v>125897311</v>
       </c>
       <c r="B20" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,37 +2437,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583915</v>
+        <v>583836</v>
       </c>
       <c r="R20" t="n">
-        <v>6963958</v>
+        <v>6963929</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2523,48 +2523,48 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897311</v>
+        <v>125888364</v>
       </c>
       <c r="B21" t="n">
-        <v>91538</v>
+        <v>101438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>221235</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583875</v>
       </c>
       <c r="R21" t="n">
-        <v>6963929</v>
+        <v>6963907</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>101435</v>
+        <v>80080</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R22" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>80040</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R23" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B24" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R24" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2914,7 +2914,7 @@
         <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97425</v>
+        <v>97428</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>98383</v>
+        <v>91538</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R32" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>91538</v>
+        <v>98386</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R33" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897313</v>
+        <v>125897326</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583852</v>
+        <v>583888</v>
       </c>
       <c r="R34" t="n">
-        <v>6963923</v>
+        <v>6963889</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897312</v>
+        <v>125897313</v>
       </c>
       <c r="B35" t="n">
         <v>91538</v>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583853</v>
+        <v>583852</v>
       </c>
       <c r="R35" t="n">
-        <v>6963924</v>
+        <v>6963923</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R36" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888356</v>
+        <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>100441</v>
+        <v>80080</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583872</v>
+        <v>583880</v>
       </c>
       <c r="R14" t="n">
-        <v>6963914</v>
+        <v>6963893</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125888464</v>
+        <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>79984</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583880</v>
+        <v>583905</v>
       </c>
       <c r="R15" t="n">
-        <v>6963893</v>
+        <v>6963925</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125887945</v>
+        <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>79984</v>
+        <v>100441</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583905</v>
+        <v>583872</v>
       </c>
       <c r="R16" t="n">
-        <v>6963925</v>
+        <v>6963914</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2135,48 +2135,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125888114</v>
+        <v>125897304</v>
       </c>
       <c r="B17" t="n">
-        <v>80080</v>
+        <v>100441</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583879</v>
+        <v>583848</v>
       </c>
       <c r="R17" t="n">
-        <v>6963918</v>
+        <v>6964006</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125888045</v>
+        <v>125888114</v>
       </c>
       <c r="B18" t="n">
         <v>80080</v>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583895</v>
+        <v>583879</v>
       </c>
       <c r="R18" t="n">
-        <v>6963945</v>
+        <v>6963918</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2329,48 +2329,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125897304</v>
+        <v>125888045</v>
       </c>
       <c r="B19" t="n">
-        <v>100441</v>
+        <v>80080</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583848</v>
+        <v>583895</v>
       </c>
       <c r="R19" t="n">
-        <v>6964006</v>
+        <v>6963945</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R23" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80080</v>
+        <v>80040</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R24" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>101438</v>
+        <v>100441</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R25" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>100441</v>
+        <v>101438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R26" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887722</v>
+        <v>125887757</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80040</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583991</v>
+        <v>583975</v>
       </c>
       <c r="R28" t="n">
-        <v>6963976</v>
+        <v>6963973</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887757</v>
+        <v>125887722</v>
       </c>
       <c r="B29" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583975</v>
+        <v>583991</v>
       </c>
       <c r="R29" t="n">
-        <v>6963973</v>
+        <v>6963976</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125897309</v>
+        <v>125887351</v>
       </c>
       <c r="B2" t="n">
-        <v>97428</v>
+        <v>80080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583962</v>
+        <v>584020</v>
       </c>
       <c r="R2" t="n">
-        <v>6964012</v>
+        <v>6963947</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125888745</v>
+        <v>125897309</v>
       </c>
       <c r="B3" t="n">
-        <v>100441</v>
+        <v>97428</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583815</v>
+        <v>583962</v>
       </c>
       <c r="R3" t="n">
-        <v>6964006</v>
+        <v>6964012</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -843,11 +843,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125887351</v>
+        <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>80080</v>
+        <v>100441</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>584020</v>
+        <v>583815</v>
       </c>
       <c r="R4" t="n">
-        <v>6963947</v>
+        <v>6964006</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -945,6 +940,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B8" t="n">
-        <v>80080</v>
+        <v>101438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R8" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>101438</v>
+        <v>100441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,37 +1370,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R9" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,48 +1456,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B10" t="n">
-        <v>100441</v>
+        <v>80080</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R10" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887805</v>
+        <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>98386</v>
+        <v>96605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583985</v>
+        <v>583908</v>
       </c>
       <c r="R11" t="n">
-        <v>6963958</v>
+        <v>6963955</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1747,32 +1747,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887998</v>
+        <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>96605</v>
+        <v>98386</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583908</v>
+        <v>583985</v>
       </c>
       <c r="R13" t="n">
-        <v>6963955</v>
+        <v>6963958</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -2135,48 +2135,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125897304</v>
+        <v>125888045</v>
       </c>
       <c r="B17" t="n">
-        <v>100441</v>
+        <v>80080</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583848</v>
+        <v>583895</v>
       </c>
       <c r="R17" t="n">
-        <v>6964006</v>
+        <v>6963945</v>
       </c>
       <c r="S17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2329,48 +2329,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125888045</v>
+        <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>80080</v>
+        <v>100441</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583895</v>
+        <v>583848</v>
       </c>
       <c r="R19" t="n">
-        <v>6963945</v>
+        <v>6964006</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2523,32 +2523,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B21" t="n">
-        <v>101438</v>
+        <v>80080</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2558,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R21" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>80080</v>
+        <v>101438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R22" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>100441</v>
+        <v>101438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R25" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>101438</v>
+        <v>100441</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R26" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887757</v>
+        <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80040</v>
+        <v>80080</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583975</v>
+        <v>583991</v>
       </c>
       <c r="R28" t="n">
-        <v>6963973</v>
+        <v>6963976</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887722</v>
+        <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80080</v>
+        <v>80040</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583991</v>
+        <v>583975</v>
       </c>
       <c r="R29" t="n">
-        <v>6963976</v>
+        <v>6963973</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B8" t="n">
-        <v>101438</v>
+        <v>100441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,37 +1273,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R8" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,48 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B9" t="n">
-        <v>100441</v>
+        <v>80080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R9" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>80080</v>
+        <v>101438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R10" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888464</v>
+        <v>125888356</v>
       </c>
       <c r="B14" t="n">
-        <v>80080</v>
+        <v>100441</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583880</v>
+        <v>583872</v>
       </c>
       <c r="R14" t="n">
-        <v>6963893</v>
+        <v>6963914</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125887945</v>
+        <v>125888464</v>
       </c>
       <c r="B15" t="n">
-        <v>79984</v>
+        <v>80080</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583905</v>
+        <v>583880</v>
       </c>
       <c r="R15" t="n">
-        <v>6963925</v>
+        <v>6963893</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125888356</v>
+        <v>125887945</v>
       </c>
       <c r="B16" t="n">
-        <v>100441</v>
+        <v>79984</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583872</v>
+        <v>583905</v>
       </c>
       <c r="R16" t="n">
-        <v>6963914</v>
+        <v>6963925</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897326</v>
+        <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>80080</v>
+        <v>91538</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583888</v>
+        <v>583852</v>
       </c>
       <c r="R34" t="n">
-        <v>6963889</v>
+        <v>6963923</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897313</v>
+        <v>125897312</v>
       </c>
       <c r="B35" t="n">
         <v>91538</v>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583852</v>
+        <v>583853</v>
       </c>
       <c r="R35" t="n">
-        <v>6963923</v>
+        <v>6963924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897312</v>
+        <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>91538</v>
+        <v>80080</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583853</v>
+        <v>583888</v>
       </c>
       <c r="R36" t="n">
-        <v>6963924</v>
+        <v>6963889</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,48 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125887351</v>
+        <v>125897309</v>
       </c>
       <c r="B2" t="n">
-        <v>80080</v>
+        <v>97437</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>584020</v>
+        <v>583962</v>
       </c>
       <c r="R2" t="n">
-        <v>6963947</v>
+        <v>6964012</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125897309</v>
+        <v>125887351</v>
       </c>
       <c r="B3" t="n">
-        <v>97428</v>
+        <v>80083</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220250</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583962</v>
+        <v>584020</v>
       </c>
       <c r="R3" t="n">
-        <v>6964012</v>
+        <v>6963947</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125888745</v>
       </c>
       <c r="B4" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>125888015</v>
       </c>
       <c r="B5" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>125888183</v>
       </c>
       <c r="B6" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>125897287</v>
       </c>
       <c r="B7" t="n">
-        <v>96605</v>
+        <v>96614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,48 +1262,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125897300</v>
+        <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>100441</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>584030</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6963845</v>
+        <v>6963902</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B9" t="n">
-        <v>80080</v>
+        <v>101447</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R9" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125887667</v>
+        <v>125897300</v>
       </c>
       <c r="B10" t="n">
-        <v>101438</v>
+        <v>100450</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583983</v>
+        <v>584030</v>
       </c>
       <c r="R10" t="n">
-        <v>6963951</v>
+        <v>6963845</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887998</v>
+        <v>125887805</v>
       </c>
       <c r="B11" t="n">
-        <v>96605</v>
+        <v>98395</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>219874</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583908</v>
+        <v>583985</v>
       </c>
       <c r="R11" t="n">
-        <v>6963955</v>
+        <v>6963958</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125888398</v>
+        <v>125887998</v>
       </c>
       <c r="B12" t="n">
-        <v>91207</v>
+        <v>96614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>53</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583876</v>
+        <v>583908</v>
       </c>
       <c r="R12" t="n">
-        <v>6963902</v>
+        <v>6963955</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887805</v>
+        <v>125888398</v>
       </c>
       <c r="B13" t="n">
-        <v>98386</v>
+        <v>91210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583985</v>
+        <v>583876</v>
       </c>
       <c r="R13" t="n">
-        <v>6963958</v>
+        <v>6963902</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1847,7 +1847,7 @@
         <v>125888356</v>
       </c>
       <c r="B14" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1944,7 +1944,7 @@
         <v>125888464</v>
       </c>
       <c r="B15" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2041,7 +2041,7 @@
         <v>125887945</v>
       </c>
       <c r="B16" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2135,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125888045</v>
+        <v>125888114</v>
       </c>
       <c r="B17" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583895</v>
+        <v>583879</v>
       </c>
       <c r="R17" t="n">
-        <v>6963945</v>
+        <v>6963918</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2232,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125888114</v>
+        <v>125888045</v>
       </c>
       <c r="B18" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,13 +2267,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583879</v>
+        <v>583895</v>
       </c>
       <c r="R18" t="n">
-        <v>6963918</v>
+        <v>6963945</v>
       </c>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2332,7 +2332,7 @@
         <v>125897304</v>
       </c>
       <c r="B19" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2426,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125897311</v>
+        <v>125888002</v>
       </c>
       <c r="B20" t="n">
-        <v>91538</v>
+        <v>80083</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2437,37 +2437,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583836</v>
+        <v>583915</v>
       </c>
       <c r="R20" t="n">
-        <v>6963929</v>
+        <v>6963958</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2523,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125888002</v>
+        <v>125897311</v>
       </c>
       <c r="B21" t="n">
-        <v>80080</v>
+        <v>91541</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,37 +2534,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583915</v>
+        <v>583836</v>
       </c>
       <c r="R21" t="n">
-        <v>6963958</v>
+        <v>6963929</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2623,7 +2623,7 @@
         <v>125888364</v>
       </c>
       <c r="B22" t="n">
-        <v>101438</v>
+        <v>101447</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80040</v>
+        <v>80043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>125897285</v>
       </c>
       <c r="B25" t="n">
-        <v>101438</v>
+        <v>101447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3011,7 +3011,7 @@
         <v>125888786</v>
       </c>
       <c r="B26" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3108,7 +3108,7 @@
         <v>125897286</v>
       </c>
       <c r="B27" t="n">
-        <v>101438</v>
+        <v>101447</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887722</v>
+        <v>125887757</v>
       </c>
       <c r="B28" t="n">
-        <v>80080</v>
+        <v>80043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583991</v>
+        <v>583975</v>
       </c>
       <c r="R28" t="n">
-        <v>6963976</v>
+        <v>6963973</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887757</v>
+        <v>125887722</v>
       </c>
       <c r="B29" t="n">
-        <v>80040</v>
+        <v>80083</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583975</v>
+        <v>583991</v>
       </c>
       <c r="R29" t="n">
-        <v>6963973</v>
+        <v>6963976</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3399,7 +3399,7 @@
         <v>125887282</v>
       </c>
       <c r="B30" t="n">
-        <v>97428</v>
+        <v>97437</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3496,7 +3496,7 @@
         <v>125887737</v>
       </c>
       <c r="B31" t="n">
-        <v>80109</v>
+        <v>80112</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>125897314</v>
       </c>
       <c r="B32" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>98386</v>
+        <v>98395</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>125897313</v>
       </c>
       <c r="B34" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>125897312</v>
       </c>
       <c r="B35" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>125897326</v>
       </c>
       <c r="B36" t="n">
-        <v>80080</v>
+        <v>80083</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4078,7 +4078,7 @@
         <v>125943980</v>
       </c>
       <c r="B37" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4175,7 +4175,7 @@
         <v>125943979</v>
       </c>
       <c r="B38" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125888370</v>
+        <v>125887667</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>101447</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583875</v>
+        <v>583983</v>
       </c>
       <c r="R8" t="n">
-        <v>6963902</v>
+        <v>6963951</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125887667</v>
+        <v>125888370</v>
       </c>
       <c r="B9" t="n">
-        <v>101447</v>
+        <v>80083</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583983</v>
+        <v>583875</v>
       </c>
       <c r="R9" t="n">
-        <v>6963951</v>
+        <v>6963902</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888356</v>
+        <v>125888464</v>
       </c>
       <c r="B14" t="n">
-        <v>100450</v>
+        <v>80083</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583872</v>
+        <v>583880</v>
       </c>
       <c r="R14" t="n">
-        <v>6963914</v>
+        <v>6963893</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125888464</v>
+        <v>125887945</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>79987</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583880</v>
+        <v>583905</v>
       </c>
       <c r="R15" t="n">
-        <v>6963893</v>
+        <v>6963925</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125887945</v>
+        <v>125888356</v>
       </c>
       <c r="B16" t="n">
-        <v>79987</v>
+        <v>100450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>222771</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583905</v>
+        <v>583872</v>
       </c>
       <c r="R16" t="n">
-        <v>6963925</v>
+        <v>6963914</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>80043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R23" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B24" t="n">
-        <v>80043</v>
+        <v>80083</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R24" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3202,32 +3202,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887757</v>
+        <v>125887722</v>
       </c>
       <c r="B28" t="n">
-        <v>80043</v>
+        <v>80083</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3237,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583975</v>
+        <v>583991</v>
       </c>
       <c r="R28" t="n">
-        <v>6963973</v>
+        <v>6963976</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3299,32 +3299,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887722</v>
+        <v>125887757</v>
       </c>
       <c r="B29" t="n">
-        <v>80083</v>
+        <v>80043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3334,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583991</v>
+        <v>583975</v>
       </c>
       <c r="R29" t="n">
-        <v>6963976</v>
+        <v>6963973</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3784,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897313</v>
+        <v>125897326</v>
       </c>
       <c r="B34" t="n">
-        <v>91541</v>
+        <v>80083</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3795,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3819,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583852</v>
+        <v>583888</v>
       </c>
       <c r="R34" t="n">
-        <v>6963923</v>
+        <v>6963889</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897312</v>
+        <v>125897313</v>
       </c>
       <c r="B35" t="n">
         <v>91541</v>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583853</v>
+        <v>583852</v>
       </c>
       <c r="R35" t="n">
-        <v>6963924</v>
+        <v>6963923</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,10 +3978,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897326</v>
+        <v>125897312</v>
       </c>
       <c r="B36" t="n">
-        <v>80083</v>
+        <v>91541</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3989,21 +3989,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583888</v>
+        <v>583853</v>
       </c>
       <c r="R36" t="n">
-        <v>6963889</v>
+        <v>6963924</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125887667</v>
+        <v>125888370</v>
       </c>
       <c r="B8" t="n">
-        <v>101447</v>
+        <v>80083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583983</v>
+        <v>583875</v>
       </c>
       <c r="R8" t="n">
-        <v>6963951</v>
+        <v>6963902</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1359,48 +1359,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125888370</v>
+        <v>125897300</v>
       </c>
       <c r="B9" t="n">
-        <v>80083</v>
+        <v>100450</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583875</v>
+        <v>584030</v>
       </c>
       <c r="R9" t="n">
-        <v>6963902</v>
+        <v>6963845</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1456,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125897300</v>
+        <v>125887667</v>
       </c>
       <c r="B10" t="n">
-        <v>100450</v>
+        <v>101447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>584030</v>
+        <v>583983</v>
       </c>
       <c r="R10" t="n">
-        <v>6963845</v>
+        <v>6963951</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1553,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887805</v>
+        <v>125887998</v>
       </c>
       <c r="B11" t="n">
-        <v>98395</v>
+        <v>96614</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219874</v>
+        <v>53</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583985</v>
+        <v>583908</v>
       </c>
       <c r="R11" t="n">
-        <v>6963958</v>
+        <v>6963955</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,32 +1650,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125887998</v>
+        <v>125888398</v>
       </c>
       <c r="B12" t="n">
-        <v>96614</v>
+        <v>91210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583908</v>
+        <v>583876</v>
       </c>
       <c r="R12" t="n">
-        <v>6963955</v>
+        <v>6963902</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125888398</v>
+        <v>125887805</v>
       </c>
       <c r="B13" t="n">
-        <v>91210</v>
+        <v>98395</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1758,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>219874</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583876</v>
+        <v>583985</v>
       </c>
       <c r="R13" t="n">
-        <v>6963902</v>
+        <v>6963958</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1844,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888464</v>
+        <v>125888356</v>
       </c>
       <c r="B14" t="n">
-        <v>80083</v>
+        <v>100450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>222771</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583880</v>
+        <v>583872</v>
       </c>
       <c r="R14" t="n">
-        <v>6963893</v>
+        <v>6963914</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,32 +1941,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125887945</v>
+        <v>125888464</v>
       </c>
       <c r="B15" t="n">
-        <v>79987</v>
+        <v>80083</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1976,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583905</v>
+        <v>583880</v>
       </c>
       <c r="R15" t="n">
-        <v>6963925</v>
+        <v>6963893</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125888356</v>
+        <v>125887945</v>
       </c>
       <c r="B16" t="n">
-        <v>100450</v>
+        <v>79987</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2049,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222771</v>
+        <v>6456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583872</v>
+        <v>583905</v>
       </c>
       <c r="R16" t="n">
-        <v>6963914</v>
+        <v>6963925</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2426,32 +2426,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888002</v>
+        <v>125888364</v>
       </c>
       <c r="B20" t="n">
-        <v>80083</v>
+        <v>101447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>221235</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2461,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>583915</v>
+        <v>583875</v>
       </c>
       <c r="R20" t="n">
-        <v>6963958</v>
+        <v>6963907</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2620,32 +2620,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888364</v>
+        <v>125888002</v>
       </c>
       <c r="B22" t="n">
-        <v>101447</v>
+        <v>80083</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583875</v>
+        <v>583915</v>
       </c>
       <c r="R22" t="n">
-        <v>6963907</v>
+        <v>6963958</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2717,32 +2717,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125888470</v>
+        <v>125887944</v>
       </c>
       <c r="B23" t="n">
-        <v>80043</v>
+        <v>80083</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229497</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583863</v>
+        <v>583906</v>
       </c>
       <c r="R23" t="n">
-        <v>6963891</v>
+        <v>6963924</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2814,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125887944</v>
+        <v>125888470</v>
       </c>
       <c r="B24" t="n">
-        <v>80083</v>
+        <v>80043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>229497</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Korallblylav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Parmeliella triptophylla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Müll.Arg.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583906</v>
+        <v>583863</v>
       </c>
       <c r="R24" t="n">
-        <v>6963924</v>
+        <v>6963891</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2911,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125897285</v>
+        <v>125888786</v>
       </c>
       <c r="B25" t="n">
-        <v>101447</v>
+        <v>100450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,37 +2922,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221235</v>
+        <v>222771</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583897</v>
+        <v>583821</v>
       </c>
       <c r="R25" t="n">
-        <v>6964003</v>
+        <v>6964002</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3008,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125888786</v>
+        <v>125897285</v>
       </c>
       <c r="B26" t="n">
-        <v>100450</v>
+        <v>101447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3019,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583821</v>
+        <v>583897</v>
       </c>
       <c r="R26" t="n">
-        <v>6964002</v>
+        <v>6964003</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897313</v>
+        <v>125897312</v>
       </c>
       <c r="B35" t="n">
         <v>91541</v>
@@ -3916,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583852</v>
+        <v>583853</v>
       </c>
       <c r="R35" t="n">
-        <v>6963923</v>
+        <v>6963924</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,7 +3978,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897312</v>
+        <v>125897313</v>
       </c>
       <c r="B36" t="n">
         <v>91541</v>
@@ -4013,10 +4013,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583853</v>
+        <v>583852</v>
       </c>
       <c r="R36" t="n">
-        <v>6963924</v>
+        <v>6963923</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125897309</v>
+        <v>125888745</v>
       </c>
       <c r="B2" t="n">
-        <v>97437</v>
+        <v>100450</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220250</v>
+        <v>222771</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583962</v>
+        <v>583815</v>
       </c>
       <c r="R2" t="n">
-        <v>6964012</v>
+        <v>6964006</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -869,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125888745</v>
+        <v>125897309</v>
       </c>
       <c r="B4" t="n">
-        <v>100450</v>
+        <v>97437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,37 +885,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222771</v>
+        <v>220250</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583815</v>
+        <v>583962</v>
       </c>
       <c r="R4" t="n">
-        <v>6964006</v>
+        <v>6964012</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -940,11 +945,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -3590,32 +3590,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B32" t="n">
-        <v>91541</v>
+        <v>98395</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R32" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S32" t="n">
         <v>25</v>
@@ -3687,32 +3687,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897322</v>
+        <v>125897314</v>
       </c>
       <c r="B33" t="n">
-        <v>98395</v>
+        <v>91541</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>219874</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583974</v>
+        <v>583871</v>
       </c>
       <c r="R33" t="n">
-        <v>6963977</v>
+        <v>6963899</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -4272,7 +4272,7 @@
         <v>130053775</v>
       </c>
       <c r="B39" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>130053332</v>
       </c>
       <c r="B40" t="n">
-        <v>92357</v>
+        <v>92359</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>130052937</v>
       </c>
       <c r="B44" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>130053404</v>
       </c>
       <c r="B45" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -4272,7 +4272,7 @@
         <v>130053775</v>
       </c>
       <c r="B39" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4369,7 +4369,7 @@
         <v>130053332</v>
       </c>
       <c r="B40" t="n">
-        <v>92359</v>
+        <v>92446</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4466,7 +4466,7 @@
         <v>130053041</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4576,7 +4576,7 @@
         <v>130052839</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4683,7 +4683,7 @@
         <v>130054422</v>
       </c>
       <c r="B43" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4790,7 +4790,7 @@
         <v>130052937</v>
       </c>
       <c r="B44" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>130053404</v>
       </c>
       <c r="B45" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
         <v>130053182</v>
       </c>
       <c r="B46" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -4887,7 +4887,7 @@
         <v>130053404</v>
       </c>
       <c r="B45" t="n">
-        <v>99013</v>
+        <v>99014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -4887,7 +4887,7 @@
         <v>130053404</v>
       </c>
       <c r="B45" t="n">
-        <v>99014</v>
+        <v>99015</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY46"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125888745</v>
+        <v>125887998</v>
       </c>
       <c r="B2" t="n">
-        <v>100450</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583815</v>
+        <v>583908</v>
       </c>
       <c r="R2" t="n">
-        <v>6964006</v>
+        <v>6963955</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-06-12</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>God förekomst</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125887351</v>
+        <v>125897287</v>
       </c>
       <c r="B3" t="n">
-        <v>80083</v>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>584020</v>
+        <v>584030</v>
       </c>
       <c r="R3" t="n">
-        <v>6963947</v>
+        <v>6963860</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125897309</v>
+        <v>125897311</v>
       </c>
       <c r="B4" t="n">
-        <v>97437</v>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220250</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583962</v>
+        <v>583836</v>
       </c>
       <c r="R4" t="n">
-        <v>6964012</v>
+        <v>6963929</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -971,48 +966,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125888015</v>
+        <v>125897312</v>
       </c>
       <c r="B5" t="n">
-        <v>80112</v>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6462</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583902</v>
+        <v>583853</v>
       </c>
       <c r="R5" t="n">
-        <v>6963960</v>
+        <v>6963924</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125888183</v>
+        <v>125897313</v>
       </c>
       <c r="B6" t="n">
-        <v>80083</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1079,37 +1074,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583882</v>
+        <v>583852</v>
       </c>
       <c r="R6" t="n">
-        <v>6963907</v>
+        <v>6963923</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125897287</v>
+        <v>125897314</v>
       </c>
       <c r="B7" t="n">
-        <v>96614</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1171,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>584030</v>
+        <v>583871</v>
       </c>
       <c r="R7" t="n">
-        <v>6963860</v>
+        <v>6963899</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1262,10 +1257,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125888370</v>
+        <v>130052937</v>
       </c>
       <c r="B8" t="n">
-        <v>80083</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,37 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583875</v>
+        <v>584003</v>
       </c>
       <c r="R8" t="n">
         <v>6963902</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1327,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1347,60 +1342,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125897300</v>
+        <v>130053775</v>
       </c>
       <c r="B9" t="n">
-        <v>100450</v>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222771</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>584030</v>
+        <v>583957</v>
       </c>
       <c r="R9" t="n">
-        <v>6963845</v>
+        <v>6964009</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1424,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1444,22 +1439,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125887667</v>
+        <v>130053332</v>
       </c>
       <c r="B10" t="n">
-        <v>101447</v>
+        <v>92632</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,37 +1462,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221235</v>
+        <v>3298</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>583983</v>
+        <v>583867</v>
       </c>
       <c r="R10" t="n">
-        <v>6963951</v>
+        <v>6963927</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1521,12 +1516,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1541,44 +1536,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125887998</v>
+        <v>125888398</v>
       </c>
       <c r="B11" t="n">
-        <v>96614</v>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>53</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583908</v>
+        <v>583876</v>
       </c>
       <c r="R11" t="n">
-        <v>6963955</v>
+        <v>6963902</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1650,10 +1645,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125888398</v>
+        <v>125887945</v>
       </c>
       <c r="B12" t="n">
-        <v>91210</v>
+        <v>80336</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1661,21 +1656,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>6456</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1685,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>583876</v>
+        <v>583905</v>
       </c>
       <c r="R12" t="n">
-        <v>6963902</v>
+        <v>6963925</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1747,32 +1742,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125887805</v>
+        <v>125887351</v>
       </c>
       <c r="B13" t="n">
-        <v>98395</v>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>219874</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1782,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>583985</v>
+        <v>584020</v>
       </c>
       <c r="R13" t="n">
-        <v>6963958</v>
+        <v>6963947</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1844,32 +1839,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125888356</v>
+        <v>125887722</v>
       </c>
       <c r="B14" t="n">
-        <v>100450</v>
+        <v>80432</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1879,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>583872</v>
+        <v>583991</v>
       </c>
       <c r="R14" t="n">
-        <v>6963914</v>
+        <v>6963976</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1941,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125888464</v>
+        <v>125887944</v>
       </c>
       <c r="B15" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1976,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>583880</v>
+        <v>583906</v>
       </c>
       <c r="R15" t="n">
-        <v>6963893</v>
+        <v>6963924</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2038,32 +2033,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125887945</v>
+        <v>125888002</v>
       </c>
       <c r="B16" t="n">
-        <v>79987</v>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6456</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2073,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>583905</v>
+        <v>583915</v>
       </c>
       <c r="R16" t="n">
-        <v>6963925</v>
+        <v>6963958</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2135,10 +2130,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125888114</v>
+        <v>125888045</v>
       </c>
       <c r="B17" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2170,13 +2165,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>583879</v>
+        <v>583895</v>
       </c>
       <c r="R17" t="n">
-        <v>6963918</v>
+        <v>6963945</v>
       </c>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2232,10 +2227,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125888045</v>
+        <v>125888114</v>
       </c>
       <c r="B18" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2267,13 +2262,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>583895</v>
+        <v>583879</v>
       </c>
       <c r="R18" t="n">
-        <v>6963945</v>
+        <v>6963918</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2329,48 +2324,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125897304</v>
+        <v>125888183</v>
       </c>
       <c r="B19" t="n">
-        <v>100450</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222771</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>583848</v>
+        <v>583882</v>
       </c>
       <c r="R19" t="n">
-        <v>6964006</v>
+        <v>6963907</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2426,32 +2421,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125888364</v>
+        <v>125888370</v>
       </c>
       <c r="B20" t="n">
-        <v>101447</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221235</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2464,7 +2459,7 @@
         <v>583875</v>
       </c>
       <c r="R20" t="n">
-        <v>6963907</v>
+        <v>6963902</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2523,10 +2518,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>125897311</v>
+        <v>125888464</v>
       </c>
       <c r="B21" t="n">
-        <v>91541</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2534,37 +2529,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>583836</v>
+        <v>583880</v>
       </c>
       <c r="R21" t="n">
-        <v>6963929</v>
+        <v>6963893</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2620,10 +2615,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>125888002</v>
+        <v>125897325</v>
       </c>
       <c r="B22" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2651,17 +2646,17 @@
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>583915</v>
+        <v>583866</v>
       </c>
       <c r="R22" t="n">
-        <v>6963958</v>
+        <v>6964017</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2717,10 +2712,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>125887944</v>
+        <v>125897326</v>
       </c>
       <c r="B23" t="n">
-        <v>80083</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2748,17 +2743,17 @@
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>583906</v>
+        <v>583888</v>
       </c>
       <c r="R23" t="n">
-        <v>6963924</v>
+        <v>6963889</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2814,10 +2809,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>125888470</v>
+        <v>125887359</v>
       </c>
       <c r="B24" t="n">
-        <v>80043</v>
+        <v>80461</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2825,21 +2820,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>229497</v>
+        <v>6462</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2849,10 +2844,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>583863</v>
+        <v>584028</v>
       </c>
       <c r="R24" t="n">
-        <v>6963891</v>
+        <v>6963943</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -2911,10 +2906,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>125888786</v>
+        <v>125887737</v>
       </c>
       <c r="B25" t="n">
-        <v>100450</v>
+        <v>80461</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2922,21 +2917,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222771</v>
+        <v>6462</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2946,10 +2941,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>583821</v>
+        <v>583971</v>
       </c>
       <c r="R25" t="n">
-        <v>6964002</v>
+        <v>6963951</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3008,10 +3003,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>125897285</v>
+        <v>125888015</v>
       </c>
       <c r="B26" t="n">
-        <v>101447</v>
+        <v>80461</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3019,37 +3014,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221235</v>
+        <v>6462</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>583897</v>
+        <v>583902</v>
       </c>
       <c r="R26" t="n">
-        <v>6964003</v>
+        <v>6963960</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3105,48 +3100,53 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>125897286</v>
+        <v>130052839</v>
       </c>
       <c r="B27" t="n">
-        <v>101447</v>
+        <v>57953</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221235</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>583838</v>
+        <v>584014</v>
       </c>
       <c r="R27" t="n">
-        <v>6963929</v>
+        <v>6963921</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3170,12 +3170,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3190,22 +3195,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>125887722</v>
+        <v>130053041</v>
       </c>
       <c r="B28" t="n">
-        <v>80083</v>
+        <v>57953</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3213,37 +3218,45 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>583991</v>
+        <v>583972</v>
       </c>
       <c r="R28" t="n">
-        <v>6963976</v>
+        <v>6963911</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3267,12 +3280,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3287,60 +3305,65 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>125887757</v>
+        <v>130053182</v>
       </c>
       <c r="B29" t="n">
-        <v>80043</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>229497</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>583975</v>
+        <v>583974</v>
       </c>
       <c r="R29" t="n">
-        <v>6963973</v>
+        <v>6963889</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3364,12 +3387,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3384,60 +3412,65 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>125887282</v>
+        <v>130054422</v>
       </c>
       <c r="B30" t="n">
-        <v>97437</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220250</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Strutbräken</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Matteuccia struthiopteris</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Tod.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>584025</v>
+        <v>584009</v>
       </c>
       <c r="R30" t="n">
-        <v>6963955</v>
+        <v>6964004</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3461,12 +3494,17 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-12-09</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack på gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3481,60 +3519,60 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>125887737</v>
+        <v>125943976</v>
       </c>
       <c r="B31" t="n">
-        <v>80112</v>
+        <v>41670</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6462</v>
+        <v>100453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Trolldruvemätare</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Baptria tibiale</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Esper, 1790)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>583971</v>
+        <v>584031</v>
       </c>
       <c r="R31" t="n">
-        <v>6963951</v>
+        <v>6963971</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3558,12 +3596,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-06-12</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3590,10 +3628,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>125897322</v>
+        <v>125887805</v>
       </c>
       <c r="B32" t="n">
-        <v>98395</v>
+        <v>99153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3621,17 +3659,17 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>583974</v>
+        <v>583985</v>
       </c>
       <c r="R32" t="n">
-        <v>6963977</v>
+        <v>6963958</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3687,32 +3725,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>125897314</v>
+        <v>125897322</v>
       </c>
       <c r="B33" t="n">
-        <v>91541</v>
+        <v>99153</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>219874</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3722,10 +3760,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>583871</v>
+        <v>583974</v>
       </c>
       <c r="R33" t="n">
-        <v>6963899</v>
+        <v>6963977</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -3784,48 +3822,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>125897326</v>
+        <v>125887282</v>
       </c>
       <c r="B34" t="n">
-        <v>80083</v>
+        <v>98186</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>220250</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Järkvissle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>583888</v>
+        <v>584025</v>
       </c>
       <c r="R34" t="n">
-        <v>6963889</v>
+        <v>6963955</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -3881,32 +3919,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>125897312</v>
+        <v>125897308</v>
       </c>
       <c r="B35" t="n">
-        <v>91541</v>
+        <v>98186</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>658</v>
+        <v>220250</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3916,10 +3954,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>583853</v>
+        <v>583955</v>
       </c>
       <c r="R35" t="n">
-        <v>6963924</v>
+        <v>6964014</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -3978,32 +4016,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>125897313</v>
+        <v>125897309</v>
       </c>
       <c r="B36" t="n">
-        <v>91541</v>
+        <v>98186</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>658</v>
+        <v>220250</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Strutbräken</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Matteuccia struthiopteris</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Tod.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4013,10 +4051,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>583852</v>
+        <v>583962</v>
       </c>
       <c r="R36" t="n">
-        <v>6963923</v>
+        <v>6964012</v>
       </c>
       <c r="S36" t="n">
         <v>25</v>
@@ -4075,48 +4113,52 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>125943980</v>
+        <v>130053404</v>
       </c>
       <c r="B37" t="n">
-        <v>100450</v>
+        <v>99118</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>222771</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>584002</v>
+        <v>583836</v>
       </c>
       <c r="R37" t="n">
-        <v>6963978</v>
+        <v>6963962</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4140,12 +4182,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4160,60 +4202,60 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>125943979</v>
+        <v>125887667</v>
       </c>
       <c r="B38" t="n">
-        <v>100450</v>
+        <v>102241</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Järkvilssle, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>583989</v>
+        <v>583983</v>
       </c>
       <c r="R38" t="n">
-        <v>6963983</v>
+        <v>6963951</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4237,12 +4279,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-06-14</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4269,48 +4311,48 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>130053775</v>
+        <v>125888364</v>
       </c>
       <c r="B39" t="n">
-        <v>92181</v>
+        <v>102241</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1209</v>
+        <v>221235</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>583957</v>
+        <v>583875</v>
       </c>
       <c r="R39" t="n">
-        <v>6964009</v>
+        <v>6963907</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4334,12 +4376,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4354,60 +4396,60 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>130053332</v>
+        <v>125897285</v>
       </c>
       <c r="B40" t="n">
-        <v>92446</v>
+        <v>102241</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>3298</v>
+        <v>221235</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>583867</v>
+        <v>583897</v>
       </c>
       <c r="R40" t="n">
-        <v>6963927</v>
+        <v>6964003</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4431,12 +4473,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4451,22 +4493,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>130053041</v>
+        <v>125897286</v>
       </c>
       <c r="B41" t="n">
-        <v>57826</v>
+        <v>102241</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4474,45 +4516,37 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>221235</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>583972</v>
+        <v>583838</v>
       </c>
       <c r="R41" t="n">
-        <v>6963911</v>
+        <v>6963929</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4536,17 +4570,12 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4561,65 +4590,60 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>130052839</v>
+        <v>125897289</v>
       </c>
       <c r="B42" t="n">
-        <v>57826</v>
+        <v>103683</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>584014</v>
+        <v>583972</v>
       </c>
       <c r="R42" t="n">
-        <v>6963921</v>
+        <v>6964019</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4643,17 +4667,12 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4668,65 +4687,60 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>130054422</v>
+        <v>125897290</v>
       </c>
       <c r="B43" t="n">
-        <v>57826</v>
+        <v>103683</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>222002</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>584009</v>
+        <v>583898</v>
       </c>
       <c r="R43" t="n">
-        <v>6964004</v>
+        <v>6964020</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -4750,17 +4764,12 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack på gran</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4775,60 +4784,60 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>130052937</v>
+        <v>125897291</v>
       </c>
       <c r="B44" t="n">
-        <v>92181</v>
+        <v>103683</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1209</v>
+        <v>222002</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Järkvissle, Mpd</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>584003</v>
+        <v>583888</v>
       </c>
       <c r="R44" t="n">
-        <v>6963902</v>
+        <v>6964017</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -4852,12 +4861,12 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -4872,64 +4881,60 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>130053404</v>
+        <v>125943977</v>
       </c>
       <c r="B45" t="n">
-        <v>99015</v>
+        <v>104628</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>222412</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Järkvilssle, Mpd</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>583836</v>
+        <v>583962</v>
       </c>
       <c r="R45" t="n">
-        <v>6963962</v>
+        <v>6964024</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -4953,12 +4958,12 @@
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -4973,65 +4978,60 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>130053182</v>
+        <v>125888356</v>
       </c>
       <c r="B46" t="n">
-        <v>57826</v>
+        <v>101228</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>222771</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Slåttmyrbäcken, Mpd</t>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>583974</v>
+        <v>583872</v>
       </c>
       <c r="R46" t="n">
-        <v>6963889</v>
+        <v>6963914</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5055,17 +5055,12 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5080,15 +5075,1281 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>125888745</v>
+      </c>
+      <c r="B47" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>583815</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6964006</v>
+      </c>
+      <c r="S47" t="n">
+        <v>20</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>God förekomst</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>125888786</v>
+      </c>
+      <c r="B48" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>583821</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6964002</v>
+      </c>
+      <c r="S48" t="n">
+        <v>20</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>125897300</v>
+      </c>
+      <c r="B49" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>584030</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6963845</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>125897301</v>
+      </c>
+      <c r="B50" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>583881</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6964017</v>
+      </c>
+      <c r="S50" t="n">
+        <v>25</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>125897302</v>
+      </c>
+      <c r="B51" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>583882</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6964018</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>125897303</v>
+      </c>
+      <c r="B52" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>583866</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6964017</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>125897304</v>
+      </c>
+      <c r="B53" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>583848</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6964006</v>
+      </c>
+      <c r="S53" t="n">
+        <v>25</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>125897305</v>
+      </c>
+      <c r="B54" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Järkvissle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>583852</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6964023</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>125943978</v>
+      </c>
+      <c r="B55" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>583962</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6964025</v>
+      </c>
+      <c r="S55" t="n">
+        <v>25</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>125943979</v>
+      </c>
+      <c r="B56" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>583989</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6963983</v>
+      </c>
+      <c r="S56" t="n">
+        <v>25</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>125943980</v>
+      </c>
+      <c r="B57" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Järkvilssle, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>584002</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6963978</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-06-14</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>125887757</v>
+      </c>
+      <c r="B58" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>583975</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6963973</v>
+      </c>
+      <c r="S58" t="n">
+        <v>20</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>125888470</v>
+      </c>
+      <c r="B59" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Slåttmyrbäcken, Slåttmyrbäcken, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>583863</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6963891</v>
+      </c>
+      <c r="S59" t="n">
+        <v>20</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Liden</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-06-12</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20708-2025 artfynd.xlsx
+++ b/artfynd/A 20708-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887998</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897287</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897311</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897312</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897313</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897314</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130052937</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053775</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053332</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888398</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887945</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887351</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887722</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887944</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888002</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888045</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888114</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888183</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888370</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888464</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897325</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,6 +2916,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897326</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2903,6 +3018,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887359</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3000,6 +3120,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887737</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3097,6 +3222,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888015</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3204,6 +3334,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130052839</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3314,6 +3449,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053041</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3421,6 +3561,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053182</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3528,6 +3673,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130054422</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3625,6 +3775,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125943976</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3722,6 +3877,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887805</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3819,6 +3979,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897322</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3916,6 +4081,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887282</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4013,6 +4183,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897308</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4110,6 +4285,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897309</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4211,6 +4391,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130053404</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4308,6 +4493,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887667</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4405,6 +4595,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888364</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4502,6 +4697,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897285</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4599,6 +4799,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897286</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4696,6 +4901,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897289</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4793,6 +5003,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897290</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4890,6 +5105,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897291</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4987,6 +5207,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125943977</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5084,6 +5309,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888356</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5186,6 +5416,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888745</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5283,6 +5518,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888786</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5380,6 +5620,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897300</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5477,6 +5722,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897301</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5574,6 +5824,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897302</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5671,6 +5926,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897303</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5768,6 +6028,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897304</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5865,6 +6130,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125897305</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -5962,6 +6232,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125943978</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6059,6 +6334,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125943979</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6156,6 +6436,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125943980</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6253,6 +6538,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125887757</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6350,8 +6640,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125888470</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>